--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261013.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261013.xlsx
@@ -821,17 +821,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>163,000</t>
+          <t>537,404</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -843,17 +843,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>537,404</t>
+          <t>163,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>12,732,134</t>
+          <t>435,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>435,000</t>
+          <t>12,732,134</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>799,897</t>
+          <t>144,921</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>144,921</t>
+          <t>799,897</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>3,440,981</t>
+          <t>3,269,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,269,000</t>
+          <t>3,440,981</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>2,567,703</t>
+          <t>385,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>385,000</t>
+          <t>2,567,703</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>7,088,249</t>
+          <t>576,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>576,000</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>7,088,249</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>767,000</t>
+          <t>2,166,107</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>2,166,107</t>
+          <t>767,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>202610WVHFV6F</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>492,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>202610WVHFV6F</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>492,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>287,000</t>
+          <t>180,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>316,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>316,000</t>
+          <t>287,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>63,538</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>1,738,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>晶豪科</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>410,000</t>
+          <t>63,538</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>晶豪科</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>1,738,000</t>
+          <t>410,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>251,000</t>
+          <t>672,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>672,000</t>
+          <t>327,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>327,000</t>
+          <t>251,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
